--- a/version1/data/Candidates.xlsx
+++ b/version1/data/Candidates.xlsx
@@ -8,7 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="Candidates" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Results" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Results_2025-05-12_01-29-30" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Results" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,10 +18,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -59,12 +57,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,6 +461,2050 @@
       <c r="C2" t="inlineStr">
         <is>
           <t>mpyd mrbx vcsj rcal</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Chandra Sai Chalicheemala</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>chandrasaichalicheemala7@gmail.com</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>iepp xrpj nbry ykyo</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Chetana Lahari Pasam</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chetanalahari057@gmail.com
+</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>mgzy myzw jbhu xlhp</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Vatsal Vadhavana</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>vadhavanavatsal@gmail.com</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ckni wtfo ampy ocza</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Naresh Linga</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>naresh.fa11@gamil.com</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ufnl paou mivy hoiu</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Ansh Patel</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ansh.fa08@gmail.com</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>laxo nabv luej osix</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Ashwinkrishnan Meialagan</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ashwinkrishnanm@gmail.com</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>axjq xuns iind iwrc</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Gunjan Singh</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>gunjanssingh86@gmail.com</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>qvxx dwns gneg tnrz</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Veera Venkata Sriram Pydi</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Veeravenkata.dve12@gmail.com</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>grvu fnps sskj tbpt</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Nilam Gajjar</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>nilam.fa10@gmail.com</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>medq wpsd plhn yssy</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Rahul Macha</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>rahul.fullstack10@gmail.com</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>zdub winy cluz lkiu</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Rafiullah Mohammed</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>rafiullah.eng786@gmail</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>rbex sanm njmw yisk</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Lokesh Babu</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>lokesh.fullstack12@gmail.com</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>jqcs savd wtyg zeba</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Aratita Chakraborty</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>aratita.pm@gmail.com</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>aojn jkzc uorv mivq</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Sai Santosh</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>santosh.fa200@gmail.com</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ahwr jieg pilf htrh</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Amisha Jain</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>amisha.financial86@gmail.com</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ehto whjs alnw twjb</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Zil Mehta</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>zilmehta86@gmail.com</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>zlcs oekz kvdg ffhp</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Jimit bhutt</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>jimitbhatt.fa@gmail.com</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>eute cfcj riui wboi</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Sai Anirudh</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>anirudhsurampudi98@gmail.com</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>bzyy eneg ydmy sugs</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Shravan Mogha</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>shravanmogha44@gmail.com</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ljio haqu sbtr vnqx</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Anirudh patil</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>anirudh.fullstack10@gmail.com</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>zdql gshg ggvv oyrx</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Pathan safrulla</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>psafrulla@gmail.com</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>ywif fnug nezq czme</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>vidhi dalwadi</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>vidhidalwadi360@gmail.com</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>pjyn vijv gkcz hqcl</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>megha subedi</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>megha.fa10@gmail.com</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>xlbb omyg gjli snyi</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Harsh Agrawal</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>harshagrawal.sdet@gmail.com</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>odkm nfiu sgya gppu</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Deekshitha Dongala</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>deekshithadongala311@gmail.com</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>gwqn utmh trmr ipao</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Venkata Mudunuri</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>venkata.fa10@gmail.com</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>jdje dlsq ithi ymal</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Devanshi Dave</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Devanshi.datanj@gmail.com</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wglw zkth pzmu jvub 
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Deepak Godi</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>deepak.fa20@gmail.com</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>rpnv qphy tnfy blvd</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>nuthan dokka</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>nuthandokka05@gmail.com</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>fehc nyhv augi ufgv</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>spandana bala</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>spandanabala2@gmail.com</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>vwgv isvz kjnk lnex</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>rutuja</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>rutujawavikar86@gmail.com</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>clju djdk kdnl igjj</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>MOHHMED ZUBAIR</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>zubair.fa10@gmail.com</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>ijam veff bssq ivhc</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>RAMYA SRI VIPPLA</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>ramyavippala69@gmail.com</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>nivg vcfm xfhu vqih</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>MALINA KARKI</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>melinakarki86@gmail.com</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>exaw ysvg okws btgl</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Deepak Sameer saikh</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>deepaksameershaik401@gmail.com</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>oluk ccpt qkpi mabk</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Uday Reddy</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>uday.net56@gmail.com</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>ppyt wvpn jfjl ckxa</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Likhith Reddy</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>likhithpallerla86@gmail.com</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>ljno sjba aonw rtht</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Shubh Goyal</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>shubh.data46@gmail.com</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>nypd vdzd myzp ymye</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hassena Shaikh</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>haseenabanushaik106@gmail.com</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>suzi kfiw jfsw uat</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Deep Patel</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>deepkumar.fa@gmail.com</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>pzli yczc saxs wnss</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Akshara Perkit</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>aksharaperkit125@gmail.com</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>qtgy anhf bisq ynyd</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Sravani Badugu</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>sravanibadugu54@gmail.com</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>kfdw lqrn qokq aiin</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Tanay Mevada</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Tanaymevada.data86@gmail.com</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>tkku scql tuqf ewkq</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Mohit Jawale</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>mohit.fullstack10@gmail.com</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>itgv yhwe kaul ldfg</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Arun Reddy</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>arunyeduguru86@gmail.com</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>jjui lhip htda zpky</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Ramachandra Raju</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>ramachandrarajup6@gmail.com</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>eyot izgv hrzg yiki</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Aryan Desai</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>desaiaryan752@gmail.com</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>fxbf owdy ccdn rmys</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Mit Rajani</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>mitjrajani86@gmail.com</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>ljqc jitx ujty tsvn</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Shiva Reddy</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>shivareddybommidika82@gmail.com</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>ncqh hdik wawb otdu</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Sapthaharsh K</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Sapthaharsh.ba10@gmail.com</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>hxgv smnp xdlu gwvs</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Aneeth Repudi</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>aneeth.devops10@gmail.com</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>pbbf rhuw mdwd kklz</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Iskuhi Parzyan</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Iskuhiparzyan95@gmail.com</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>qhal hlms wuat lnbe</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Partha Sai Guttikonda</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>parthasai33@gmail.com</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>jufw xvmo axqj heaa</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Kavyasri Avushapuram</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Kavyasri.de@gmail.com</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>djjl ncxv qkwx jbmv</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Betty Umeh</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>BettyUmeh86@gmail.com</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>jozv spzf gvyp pjdo</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Harshil Thakkar</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>harshilthakkar78@gmail.com</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>atbf rgtm flaf aiwe</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>SaiPrudhviRaj G</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>saiprudhviraj11@gmail.com</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>wcmq eyqc ckll dnle</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Sai Sandeep Challagolla</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>saisandeep.fa@gmail.com</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>coel tvat emrz gqmf</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Atithi Prasai</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>prasaiatithi09@gmail.com</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>hydo lzpi ahfz rlcf</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Sai Dinesh Ganja</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>saidineshganja12@gmail.com</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>dvzu eopa qiwc sdub</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Reyaan Shaik</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>reyaanshaik66@gmail.com</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>mayw zeoa ijhg niqq</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Gopichand Jonnalagadda</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>gopichandjonnalgadda53@gmail.com</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>caus jraz keai yfks</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Srija Gunturu</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>srijagunturu99@gmail.com</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>hgla wepj vysm akye</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Kalyan Kumar Thula</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>kalyankthula96@gmail.com</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>duff ylid hpcl kvrh</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Neha Shah</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>neha.finance86@gmail.com</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>bstt wthh aaya ccvc</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Apoorv Singh</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>apoorv.financial46@gmail.com</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>ljuc awsr ibki xwhn</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Vnittha Reddy Kondakalla</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>vinithareddy207@gmail.com</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>msqn pwts dlow bzjq</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Partha Mehta</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>parth.fa09@gmail.com</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>kgvs ghqc ehxf zxkk</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Surya Bhaskar</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>bhaskarsurya925@gmail.com</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>angm lgkc tkce ymap</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Kunjal Patel</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>kunjal.fullstack@gmail.com</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>angh qlol bkji nerh</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Smitha Nair</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>smithannair86@gmail.com</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>fqgu aqam pddy fmlt</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Sheila Udoji</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>sheilaudoji11@gmail.com</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>drrq fcsu slzc wifa</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Pratiksha Pawar</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Pratiksha.BApawar86@gmail.com</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>chvd uupl mlzv rsag</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Haritha Danda</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>harithadataeng@gmail.com</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>neit lubh logp smik</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Adithya Prasad</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>adithyaprasad213@gmail.com</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>hoeb xvlw omaj pmkk</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Nishant Sironjiya</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>nishant.fa10@gmail.com</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>kvrd vwmv hbgc rktq</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Ram Naresh Balagani</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Ramnaresh.fullstack@gmail.com</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>jdlf jwgl lrhe ufsd</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>sai monisha</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">saimounishagurram@gmail.com 
+</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>zpke nchj tzjg yncv</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>akhil teja</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>akhilateja86@gmail.com</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>verw wpvt fbmi ymbm</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>sravani</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>sravanivarikuti01@gmail.com</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gkgo bbku taif xiez 
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Kaushakl</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>kaushal.fa10@gmail.com</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>iqge jaga lcpe dudq</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Shivani Rajole</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>shivani.qa10@gmail.com</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>qvkd todz abui wvfz</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Ramesh Basakonda</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>rameshbasakonda7@gmail.com</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>umau diue vomc ghwp</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>NagendraKumar</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Nagendrakumar.data86@gmail.com</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>elph fcjm murj rwsm</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Vanamala Bhargav</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>bhargav.ml188@gmail.com</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>nok drop hztm bdtq</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Harika Boddu</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>harikaboddu76@gmail.com</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>tprs frrg pdih rene</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>KAHAN DAVE</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>kahandave36@gmail.com</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>uhfa qswj fsla oesz</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Sravani T.</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>sravanisankar924@gmail.com</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>vutw lnfx pled wwgk</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Polepaka Arun Abishake</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>arun.devopseng80@gmail.com</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>thuf kvsr hycp dxsq</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Harsh Trivedi</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Harsh.financial86@gmail.com</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>wrzc aoau ylcj eigi</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>malhar gate</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>malhargate9@gmail.com</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>arno tzlq bewr pelf</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Mounika Davuluri</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>mounika.dataeng27@gmail.com</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>dijl hulh onqk guzl</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Emeka</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>emekanwude86@gmail.com</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>gjeo qerw rfpg ctga</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Emeka</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>nwudeemeka0@gmail.com</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>dgkr siof htcp ppbf</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Parth Patel</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>paarthpatel1998@gmail.com</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>hgpb ybvz fxio avmv</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Aman coiro</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>amancoiro.desktop@gmail.com</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>ieli cfkj hwrz tvsw</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Fnu Neeraj</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>neeraj.uiux1@gmail.com</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>fvmi mwyg onfp aopl</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Akhilesh Kontham</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>akhileshkontham213@gmail.com</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>nyus usup bkkf dkzw</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Irfan ali</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>irfanservice.dev27@gmail.com</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>gawm dekz hxak tdgd</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Shreelekha</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>shreelekhaaduraiswamy2@gmail.com</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>csxd yrgk godu szpr</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Amar Lingarao</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>amar.fullstack1@gmail.com</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>ryid hyqb ucds ejxh</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Sivani koneti</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>dev.shivanik@gmail.com</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>uewv brwp arwf eiwu</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Mehul kumar</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>mehul.pm10@gmail.com</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>pnnu irob dbyp vhmy</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Spoorthy Ayyagari</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>spoorthyayyagari08@gmail.com</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>airx naod tioe hjya</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Akanksh Chinthalapally</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>akankshfin07@gmail.com</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>otgz krgc qoww xhaw</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Darshil Patel</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>darshil.eng08@gmail.com</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>bogi emxq whwo gyoj</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Suryakanth Jonnalagadda</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>suryakanth.customersuccess@gmail.com</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>mtxg bnxn zqig syxi</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Rohan Benhal</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>benhalrohan@gmail.com</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>otra bwcm jbqt kqnn</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Hansil Patel</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>hansilpatel86@gmail.com</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>hdse wqcr ammx ojua</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Harshil sanghavi</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>harshilsanghavi86@gmail.com</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>ushx vneq bsdw ikxi</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Rishi Rudrabhatla</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Rishirudrabhatla45@gmail.com</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>ixqt ympe sklg zcqq</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Nithish Kumar Reddy</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>nithishthigala@gmail.com</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>vkjg nmzf wtmd hvsy</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>hari krishna chirumamilla</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>harifullstack.dev27@gmail.com</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>eqor lgmp ggge pedt</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>charan yalamuri</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>venkatcharanyalamuri@gmail.com</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>ztoe eyzp fjzj oret</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Vishal Balaji</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>balajigithendra2025@gmail.com</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>jsip wxmf vuyy xnqx</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Prasanna</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>pathuriprasanna226@gmail.com</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>flhr csfb xius sjwn</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>shreelaasya</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>vshreelaasya5@gmail.com</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>fofz liww lbwy jgrg</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Naveen</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>naveenkumarl1361@gmail.com</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>hhdj zufw vqij kywp</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>MIRZA ASGAR ALI</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>aliasgar.fs10@gmail.com</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>ejyf npkv bndz cnmg</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Aashish Hemanth Masuna</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>ashishhemanth1@gmail.com</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>onim zsab qctw etxb</t>
         </is>
       </c>
     </row>
@@ -478,7 +2519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -533,40 +2574,70 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>KRML</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>keerthiraj.k0222@gmail.com</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>6</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>2</v>
-      </c>
-      <c r="I2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>45786.68532599785</v>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>CandidateId</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>CandidateName</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>CandidateEmail</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Application</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Interview</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Offer</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Rejection</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>LastUpdated</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/version1/data/Candidates.xlsx
+++ b/version1/data/Candidates.xlsx
@@ -8,19 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\keert\OneDrive\Desktop\KEERTHIRAJ\PROJECTS\Email-Automation\version1\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{884A03F3-2381-4B8C-A159-C155BAFBC2CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{668D60B6-C682-4F03-813D-DD123D4E2FF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Candidates" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="364">
   <si>
     <t>Name</t>
   </si>
@@ -29,15 +30,6 @@
   </si>
   <si>
     <t>candidatePassword__c</t>
-  </si>
-  <si>
-    <t>KRML</t>
-  </si>
-  <si>
-    <t>keerthiraj.k0222@gmail.com</t>
-  </si>
-  <si>
-    <t>mpyd mrbx vcsj rcal</t>
   </si>
   <si>
     <t>Chetana Lahari Pasam</t>
@@ -48,6 +40,1083 @@
   </si>
   <si>
     <t>mgzy myzw jbhu xlhp</t>
+  </si>
+  <si>
+    <t>Chandra Sai Chalicheemala</t>
+  </si>
+  <si>
+    <t>chandrasaichalicheemala7@gmail.com</t>
+  </si>
+  <si>
+    <t>iepp xrpj nbry ykyo</t>
+  </si>
+  <si>
+    <t>Vatsal Vadhavana</t>
+  </si>
+  <si>
+    <t>vadhavanavatsal@gmail.com</t>
+  </si>
+  <si>
+    <t>ckni wtfo ampy ocza</t>
+  </si>
+  <si>
+    <t>Naresh Linga</t>
+  </si>
+  <si>
+    <t>naresh.fa11@gamil.com</t>
+  </si>
+  <si>
+    <t>ufnl paou mivy hoiu</t>
+  </si>
+  <si>
+    <t>Ansh Patel</t>
+  </si>
+  <si>
+    <t>ansh.fa08@gmail.com</t>
+  </si>
+  <si>
+    <t>laxo nabv luej osix</t>
+  </si>
+  <si>
+    <t>Sai Rithwik</t>
+  </si>
+  <si>
+    <t>sairithwikreddybolla@gmail.com</t>
+  </si>
+  <si>
+    <t>Ashwinkrishnan Meialagan</t>
+  </si>
+  <si>
+    <t>ashwinkrishnanm@gmail.com</t>
+  </si>
+  <si>
+    <t>axjq xuns iind iwrc</t>
+  </si>
+  <si>
+    <t>Gunjan Singh</t>
+  </si>
+  <si>
+    <t>gunjanssingh86@gmail.com</t>
+  </si>
+  <si>
+    <t>qvxx dwns gneg tnrz</t>
+  </si>
+  <si>
+    <t>Veera Venkata Sriram Pydi</t>
+  </si>
+  <si>
+    <t>Veeravenkata.dve12@gmail.com</t>
+  </si>
+  <si>
+    <t>grvu fnps sskj tbpt</t>
+  </si>
+  <si>
+    <t>Nilam Gajjar</t>
+  </si>
+  <si>
+    <t>nilam.fa10@gmail.com</t>
+  </si>
+  <si>
+    <t>medq wpsd plhn yssy</t>
+  </si>
+  <si>
+    <t>Rahul Macha</t>
+  </si>
+  <si>
+    <t>rahul.fullstack10@gmail.com</t>
+  </si>
+  <si>
+    <t>zdub winy cluz lkiu</t>
+  </si>
+  <si>
+    <t>Rafiullah Mohammed</t>
+  </si>
+  <si>
+    <t>rafiullah.eng786@gmail</t>
+  </si>
+  <si>
+    <t>rbex sanm njmw yisk</t>
+  </si>
+  <si>
+    <t>Lokesh Babu</t>
+  </si>
+  <si>
+    <t>lokesh.fullstack12@gmail.com</t>
+  </si>
+  <si>
+    <t>jqcs savd wtyg zeba</t>
+  </si>
+  <si>
+    <t>Aratita Chakraborty</t>
+  </si>
+  <si>
+    <t>aratita.pm@gmail.com</t>
+  </si>
+  <si>
+    <t>aojn jkzc uorv mivq</t>
+  </si>
+  <si>
+    <t>Sai Santosh</t>
+  </si>
+  <si>
+    <t>santosh.fa200@gmail.com</t>
+  </si>
+  <si>
+    <t>ahwr jieg pilf htrh</t>
+  </si>
+  <si>
+    <t>Amisha Jain</t>
+  </si>
+  <si>
+    <t>amisha.financial86@gmail.com</t>
+  </si>
+  <si>
+    <t>ehto whjs alnw twjb</t>
+  </si>
+  <si>
+    <t>Zil Mehta</t>
+  </si>
+  <si>
+    <t>zilmehta86@gmail.com</t>
+  </si>
+  <si>
+    <t>zlcs oekz kvdg ffhp</t>
+  </si>
+  <si>
+    <t>Jimit bhutt</t>
+  </si>
+  <si>
+    <t>jimitbhatt.fa@gmail.com</t>
+  </si>
+  <si>
+    <t>eute cfcj riui wboi</t>
+  </si>
+  <si>
+    <t>Sai Anirudh</t>
+  </si>
+  <si>
+    <t>anirudhsurampudi98@gmail.com</t>
+  </si>
+  <si>
+    <t>bzyy eneg ydmy sugs</t>
+  </si>
+  <si>
+    <t>Shravan Mogha</t>
+  </si>
+  <si>
+    <t>shravanmogha44@gmail.com</t>
+  </si>
+  <si>
+    <t>ljio haqu sbtr vnqx</t>
+  </si>
+  <si>
+    <t>Anirudh patil</t>
+  </si>
+  <si>
+    <t>anirudh.fullstack10@gmail.com</t>
+  </si>
+  <si>
+    <t>zdql gshg ggvv oyrx</t>
+  </si>
+  <si>
+    <t>Pathan safrulla</t>
+  </si>
+  <si>
+    <t>psafrulla@gmail.com</t>
+  </si>
+  <si>
+    <t>ywif fnug nezq czme</t>
+  </si>
+  <si>
+    <t>vidhi dalwadi</t>
+  </si>
+  <si>
+    <t>vidhidalwadi360@gmail.com</t>
+  </si>
+  <si>
+    <t>pjyn vijv gkcz hqcl</t>
+  </si>
+  <si>
+    <t>megha subedi</t>
+  </si>
+  <si>
+    <t>megha.fa10@gmail.com</t>
+  </si>
+  <si>
+    <t>xlbb omyg gjli snyi</t>
+  </si>
+  <si>
+    <t>Harsh Agrawal</t>
+  </si>
+  <si>
+    <t>harshagrawal.sdet@gmail.com</t>
+  </si>
+  <si>
+    <t>odkm nfiu sgya gppu</t>
+  </si>
+  <si>
+    <t>Deekshitha Dongala</t>
+  </si>
+  <si>
+    <t>deekshithadongala311@gmail.com</t>
+  </si>
+  <si>
+    <t>gwqn utmh trmr ipao</t>
+  </si>
+  <si>
+    <t>Venkata Mudunuri</t>
+  </si>
+  <si>
+    <t>venkata.fa10@gmail.com</t>
+  </si>
+  <si>
+    <t>jdje dlsq ithi ymal</t>
+  </si>
+  <si>
+    <t>Devanshi Dave</t>
+  </si>
+  <si>
+    <t>Devanshi.datanj@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wglw zkth pzmu jvub 
+</t>
+  </si>
+  <si>
+    <t>Deepak Godi</t>
+  </si>
+  <si>
+    <t>deepak.fa20@gmail.com</t>
+  </si>
+  <si>
+    <t>rpnv qphy tnfy blvd</t>
+  </si>
+  <si>
+    <t>nuthan dokka</t>
+  </si>
+  <si>
+    <t>nuthandokka05@gmail.com</t>
+  </si>
+  <si>
+    <t>fehc nyhv augi ufgv</t>
+  </si>
+  <si>
+    <t>spandana bala</t>
+  </si>
+  <si>
+    <t>spandanabala2@gmail.com</t>
+  </si>
+  <si>
+    <t>vwgv isvz kjnk lnex</t>
+  </si>
+  <si>
+    <t>rutuja</t>
+  </si>
+  <si>
+    <t>rutujawavikar86@gmail.com</t>
+  </si>
+  <si>
+    <t>clju djdk kdnl igjj</t>
+  </si>
+  <si>
+    <t>MOHHMED ZUBAIR</t>
+  </si>
+  <si>
+    <t>zubair.fa10@gmail.com</t>
+  </si>
+  <si>
+    <t>ijam veff bssq ivhc</t>
+  </si>
+  <si>
+    <t>RAMYA SRI VIPPLA</t>
+  </si>
+  <si>
+    <t>ramyavippala69@gmail.com</t>
+  </si>
+  <si>
+    <t>nivg vcfm xfhu vqih</t>
+  </si>
+  <si>
+    <t>MALINA KARKI</t>
+  </si>
+  <si>
+    <t>melinakarki86@gmail.com</t>
+  </si>
+  <si>
+    <t>exaw ysvg okws btgl</t>
+  </si>
+  <si>
+    <t>Deepak Sameer saikh</t>
+  </si>
+  <si>
+    <t>deepaksameershaik401@gmail.com</t>
+  </si>
+  <si>
+    <t>oluk ccpt qkpi mabk</t>
+  </si>
+  <si>
+    <t>Uday Reddy</t>
+  </si>
+  <si>
+    <t>uday.net56@gmail.com</t>
+  </si>
+  <si>
+    <t>ppyt wvpn jfjl ckxa</t>
+  </si>
+  <si>
+    <t>Likhith Reddy</t>
+  </si>
+  <si>
+    <t>likhithpallerla86@gmail.com</t>
+  </si>
+  <si>
+    <t>ljno sjba aonw rtht</t>
+  </si>
+  <si>
+    <t>Shubh Goyal</t>
+  </si>
+  <si>
+    <t>shubh.data46@gmail.com</t>
+  </si>
+  <si>
+    <t>nypd vdzd myzp ymye</t>
+  </si>
+  <si>
+    <t>Hassena Shaikh</t>
+  </si>
+  <si>
+    <t>haseenabanushaik106@gmail.com</t>
+  </si>
+  <si>
+    <t>suzi kfiw jfsw uat</t>
+  </si>
+  <si>
+    <t>Deep Patel</t>
+  </si>
+  <si>
+    <t>deepkumar.fa@gmail.com</t>
+  </si>
+  <si>
+    <t>pzli yczc saxs wnss</t>
+  </si>
+  <si>
+    <t>Akshara Perkit</t>
+  </si>
+  <si>
+    <t>aksharaperkit125@gmail.com</t>
+  </si>
+  <si>
+    <t>qtgy anhf bisq ynyd</t>
+  </si>
+  <si>
+    <t>Sravani Badugu</t>
+  </si>
+  <si>
+    <t>sravanibadugu54@gmail.com</t>
+  </si>
+  <si>
+    <t>kfdw lqrn qokq aiin</t>
+  </si>
+  <si>
+    <t>Tanay Mevada</t>
+  </si>
+  <si>
+    <t>Tanaymevada.data86@gmail.com</t>
+  </si>
+  <si>
+    <t>tkku scql tuqf ewkq</t>
+  </si>
+  <si>
+    <t>Mohit Jawale</t>
+  </si>
+  <si>
+    <t>mohit.fullstack10@gmail.com</t>
+  </si>
+  <si>
+    <t>itgv yhwe kaul ldfg</t>
+  </si>
+  <si>
+    <t>Arun Reddy</t>
+  </si>
+  <si>
+    <t>arunyeduguru86@gmail.com</t>
+  </si>
+  <si>
+    <t>jjui lhip htda zpky</t>
+  </si>
+  <si>
+    <t>Ramachandra Raju</t>
+  </si>
+  <si>
+    <t>ramachandrarajup6@gmail.com</t>
+  </si>
+  <si>
+    <t>eyot izgv hrzg yiki</t>
+  </si>
+  <si>
+    <t>Aryan Desai</t>
+  </si>
+  <si>
+    <t>desaiaryan752@gmail.com</t>
+  </si>
+  <si>
+    <t>fxbf owdy ccdn rmys</t>
+  </si>
+  <si>
+    <t>Mit Rajani</t>
+  </si>
+  <si>
+    <t>mitjrajani86@gmail.com</t>
+  </si>
+  <si>
+    <t>ljqc jitx ujty tsvn</t>
+  </si>
+  <si>
+    <t>Shiva Reddy</t>
+  </si>
+  <si>
+    <t>shivareddybommidika82@gmail.com</t>
+  </si>
+  <si>
+    <t>ncqh hdik wawb otdu</t>
+  </si>
+  <si>
+    <t>Sapthaharsh K</t>
+  </si>
+  <si>
+    <t>Sapthaharsh.ba10@gmail.com</t>
+  </si>
+  <si>
+    <t>hxgv smnp xdlu gwvs</t>
+  </si>
+  <si>
+    <t>Aneeth Repudi</t>
+  </si>
+  <si>
+    <t>aneeth.devops10@gmail.com</t>
+  </si>
+  <si>
+    <t>pbbf rhuw mdwd kklz</t>
+  </si>
+  <si>
+    <t>Iskuhi Parzyan</t>
+  </si>
+  <si>
+    <t>Iskuhiparzyan95@gmail.com</t>
+  </si>
+  <si>
+    <t>qhal hlms wuat lnbe</t>
+  </si>
+  <si>
+    <t>Partha Sai Guttikonda</t>
+  </si>
+  <si>
+    <t>parthasai33@gmail.com</t>
+  </si>
+  <si>
+    <t>jufw xvmo axqj heaa</t>
+  </si>
+  <si>
+    <t>Kavyasri Avushapuram</t>
+  </si>
+  <si>
+    <t>Kavyasri.de@gmail.com</t>
+  </si>
+  <si>
+    <t>djjl ncxv qkwx jbmv</t>
+  </si>
+  <si>
+    <t>Betty Umeh</t>
+  </si>
+  <si>
+    <t>BettyUmeh86@gmail.com</t>
+  </si>
+  <si>
+    <t>jozv spzf gvyp pjdo</t>
+  </si>
+  <si>
+    <t>Harshil Thakkar</t>
+  </si>
+  <si>
+    <t>harshilthakkar78@gmail.com</t>
+  </si>
+  <si>
+    <t>atbf rgtm flaf aiwe</t>
+  </si>
+  <si>
+    <t>SaiPrudhviRaj G</t>
+  </si>
+  <si>
+    <t>saiprudhviraj11@gmail.com</t>
+  </si>
+  <si>
+    <t>wcmq eyqc ckll dnle</t>
+  </si>
+  <si>
+    <t>Sai Sandeep Challagolla</t>
+  </si>
+  <si>
+    <t>saisandeep.fa@gmail.com</t>
+  </si>
+  <si>
+    <t>coel tvat emrz gqmf</t>
+  </si>
+  <si>
+    <t>Atithi Prasai</t>
+  </si>
+  <si>
+    <t>prasaiatithi09@gmail.com</t>
+  </si>
+  <si>
+    <t>hydo lzpi ahfz rlcf</t>
+  </si>
+  <si>
+    <t>Sai Dinesh Ganja</t>
+  </si>
+  <si>
+    <t>saidineshganja12@gmail.com</t>
+  </si>
+  <si>
+    <t>dvzu eopa qiwc sdub</t>
+  </si>
+  <si>
+    <t>Reyaan Shaik</t>
+  </si>
+  <si>
+    <t>reyaanshaik66@gmail.com</t>
+  </si>
+  <si>
+    <t>mayw zeoa ijhg niqq</t>
+  </si>
+  <si>
+    <t>Gopichand Jonnalagadda</t>
+  </si>
+  <si>
+    <t>gopichandjonnalgadda53@gmail.com</t>
+  </si>
+  <si>
+    <t>caus jraz keai yfks</t>
+  </si>
+  <si>
+    <t>Srija Gunturu</t>
+  </si>
+  <si>
+    <t>srijagunturu99@gmail.com</t>
+  </si>
+  <si>
+    <t>hgla wepj vysm akye</t>
+  </si>
+  <si>
+    <t>Kalyan Kumar Thula</t>
+  </si>
+  <si>
+    <t>kalyankthula96@gmail.com</t>
+  </si>
+  <si>
+    <t>duff ylid hpcl kvrh</t>
+  </si>
+  <si>
+    <t>Neha Shah</t>
+  </si>
+  <si>
+    <t>neha.finance86@gmail.com</t>
+  </si>
+  <si>
+    <t>bstt wthh aaya ccvc</t>
+  </si>
+  <si>
+    <t>Apoorv Singh</t>
+  </si>
+  <si>
+    <t>apoorv.financial46@gmail.com</t>
+  </si>
+  <si>
+    <t>ljuc awsr ibki xwhn</t>
+  </si>
+  <si>
+    <t>Vnittha Reddy Kondakalla</t>
+  </si>
+  <si>
+    <t>vinithareddy207@gmail.com</t>
+  </si>
+  <si>
+    <t>msqn pwts dlow bzjq</t>
+  </si>
+  <si>
+    <t>Partha Mehta</t>
+  </si>
+  <si>
+    <t>parth.fa09@gmail.com</t>
+  </si>
+  <si>
+    <t>kgvs ghqc ehxf zxkk</t>
+  </si>
+  <si>
+    <t>Surya Bhaskar</t>
+  </si>
+  <si>
+    <t>bhaskarsurya925@gmail.com</t>
+  </si>
+  <si>
+    <t>angm lgkc tkce ymap</t>
+  </si>
+  <si>
+    <t>Kunjal Patel</t>
+  </si>
+  <si>
+    <t>kunjal.fullstack@gmail.com</t>
+  </si>
+  <si>
+    <t>angh qlol bkji nerh</t>
+  </si>
+  <si>
+    <t>Smitha Nair</t>
+  </si>
+  <si>
+    <t>smithannair86@gmail.com</t>
+  </si>
+  <si>
+    <t>fqgu aqam pddy fmlt</t>
+  </si>
+  <si>
+    <t>Sheila Udoji</t>
+  </si>
+  <si>
+    <t>sheilaudoji11@gmail.com</t>
+  </si>
+  <si>
+    <t>drrq fcsu slzc wifa</t>
+  </si>
+  <si>
+    <t>Pratiksha Pawar</t>
+  </si>
+  <si>
+    <t>Pratiksha.BApawar86@gmail.com</t>
+  </si>
+  <si>
+    <t>chvd uupl mlzv rsag</t>
+  </si>
+  <si>
+    <t>Haritha Danda</t>
+  </si>
+  <si>
+    <t>harithadataeng@gmail.com</t>
+  </si>
+  <si>
+    <t>neit lubh logp smik</t>
+  </si>
+  <si>
+    <t>Adithya Prasad</t>
+  </si>
+  <si>
+    <t>adithyaprasad213@gmail.com</t>
+  </si>
+  <si>
+    <t>hoeb xvlw omaj pmkk</t>
+  </si>
+  <si>
+    <t>Nishant Sironjiya</t>
+  </si>
+  <si>
+    <t>nishant.fa10@gmail.com</t>
+  </si>
+  <si>
+    <t>kvrd vwmv hbgc rktq</t>
+  </si>
+  <si>
+    <t>Ram Naresh Balagani</t>
+  </si>
+  <si>
+    <t>Ramnaresh.fullstack@gmail.com</t>
+  </si>
+  <si>
+    <t>jdlf jwgl lrhe ufsd</t>
+  </si>
+  <si>
+    <t>sai monisha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">saimounishagurram@gmail.com 
+</t>
+  </si>
+  <si>
+    <t>zpke nchj tzjg yncv</t>
+  </si>
+  <si>
+    <t>akhil teja</t>
+  </si>
+  <si>
+    <t>akhilateja86@gmail.com</t>
+  </si>
+  <si>
+    <t>verw wpvt fbmi ymbm</t>
+  </si>
+  <si>
+    <t>sravani</t>
+  </si>
+  <si>
+    <t>sravanivarikuti01@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gkgo bbku taif xiez 
+</t>
+  </si>
+  <si>
+    <t>Kaushakl</t>
+  </si>
+  <si>
+    <t>kaushal.fa10@gmail.com</t>
+  </si>
+  <si>
+    <t>iqge jaga lcpe dudq</t>
+  </si>
+  <si>
+    <t>Shivani Rajole</t>
+  </si>
+  <si>
+    <t>shivani.qa10@gmail.com</t>
+  </si>
+  <si>
+    <t>qvkd todz abui wvfz</t>
+  </si>
+  <si>
+    <t>Ramesh Basakonda</t>
+  </si>
+  <si>
+    <t>rameshbasakonda7@gmail.com</t>
+  </si>
+  <si>
+    <t>umau diue vomc ghwp</t>
+  </si>
+  <si>
+    <t>NagendraKumar</t>
+  </si>
+  <si>
+    <t>Nagendrakumar.data86@gmail.com</t>
+  </si>
+  <si>
+    <t>elph fcjm murj rwsm</t>
+  </si>
+  <si>
+    <t>Vanamala Bhargav</t>
+  </si>
+  <si>
+    <t>bhargav.ml188@gmail.com</t>
+  </si>
+  <si>
+    <t>nok drop hztm bdtq</t>
+  </si>
+  <si>
+    <t>Harika Boddu</t>
+  </si>
+  <si>
+    <t>harikaboddu76@gmail.com</t>
+  </si>
+  <si>
+    <t>tprs frrg pdih rene</t>
+  </si>
+  <si>
+    <t>KAHAN DAVE</t>
+  </si>
+  <si>
+    <t>kahandave36@gmail.com</t>
+  </si>
+  <si>
+    <t>uhfa qswj fsla oesz</t>
+  </si>
+  <si>
+    <t>Sravani T.</t>
+  </si>
+  <si>
+    <t>sravanisankar924@gmail.com</t>
+  </si>
+  <si>
+    <t>vutw lnfx pled wwgk</t>
+  </si>
+  <si>
+    <t>Polepaka Arun Abishake</t>
+  </si>
+  <si>
+    <t>arun.devopseng80@gmail.com</t>
+  </si>
+  <si>
+    <t>thuf kvsr hycp dxsq</t>
+  </si>
+  <si>
+    <t>Harsh Trivedi</t>
+  </si>
+  <si>
+    <t>Harsh.financial86@gmail.com</t>
+  </si>
+  <si>
+    <t>wrzc aoau ylcj eigi</t>
+  </si>
+  <si>
+    <t>malhar gate</t>
+  </si>
+  <si>
+    <t>malhargate9@gmail.com</t>
+  </si>
+  <si>
+    <t>arno tzlq bewr pelf</t>
+  </si>
+  <si>
+    <t>Mounika Davuluri</t>
+  </si>
+  <si>
+    <t>mounika.dataeng27@gmail.com</t>
+  </si>
+  <si>
+    <t>dijl hulh onqk guzl</t>
+  </si>
+  <si>
+    <t>Emeka</t>
+  </si>
+  <si>
+    <t>emekanwude86@gmail.com</t>
+  </si>
+  <si>
+    <t>gjeo qerw rfpg ctga</t>
+  </si>
+  <si>
+    <t>nwudeemeka0@gmail.com</t>
+  </si>
+  <si>
+    <t>dgkr siof htcp ppbf</t>
+  </si>
+  <si>
+    <t>Parth Patel</t>
+  </si>
+  <si>
+    <t>paarthpatel1998@gmail.com</t>
+  </si>
+  <si>
+    <t>hgpb ybvz fxio avmv</t>
+  </si>
+  <si>
+    <t>Aman coiro</t>
+  </si>
+  <si>
+    <t>amancoiro.desktop@gmail.com</t>
+  </si>
+  <si>
+    <t>ieli cfkj hwrz tvsw</t>
+  </si>
+  <si>
+    <t>Fnu Neeraj</t>
+  </si>
+  <si>
+    <t>neeraj.uiux1@gmail.com</t>
+  </si>
+  <si>
+    <t>fvmi mwyg onfp aopl</t>
+  </si>
+  <si>
+    <t>Akhilesh Kontham</t>
+  </si>
+  <si>
+    <t>akhileshkontham213@gmail.com</t>
+  </si>
+  <si>
+    <t>nyus usup bkkf dkzw</t>
+  </si>
+  <si>
+    <t>Irfan ali</t>
+  </si>
+  <si>
+    <t>irfanservice.dev27@gmail.com</t>
+  </si>
+  <si>
+    <t>gawm dekz hxak tdgd</t>
+  </si>
+  <si>
+    <t>Shreelekha</t>
+  </si>
+  <si>
+    <t>shreelekhaaduraiswamy2@gmail.com</t>
+  </si>
+  <si>
+    <t>csxd yrgk godu szpr</t>
+  </si>
+  <si>
+    <t>Amar Lingarao</t>
+  </si>
+  <si>
+    <t>amar.fullstack1@gmail.com</t>
+  </si>
+  <si>
+    <t>ryid hyqb ucds ejxh</t>
+  </si>
+  <si>
+    <t>Sivani koneti</t>
+  </si>
+  <si>
+    <t>dev.shivanik@gmail.com</t>
+  </si>
+  <si>
+    <t>uewv brwp arwf eiwu</t>
+  </si>
+  <si>
+    <t>Mehul kumar</t>
+  </si>
+  <si>
+    <t>mehul.pm10@gmail.com</t>
+  </si>
+  <si>
+    <t>pnnu irob dbyp vhmy</t>
+  </si>
+  <si>
+    <t>Spoorthy Ayyagari</t>
+  </si>
+  <si>
+    <t>spoorthyayyagari08@gmail.com</t>
+  </si>
+  <si>
+    <t>airx naod tioe hjya</t>
+  </si>
+  <si>
+    <t>Akanksh Chinthalapally</t>
+  </si>
+  <si>
+    <t>akankshfin07@gmail.com</t>
+  </si>
+  <si>
+    <t>otgz krgc qoww xhaw</t>
+  </si>
+  <si>
+    <t>Darshil Patel</t>
+  </si>
+  <si>
+    <t>darshil.eng08@gmail.com</t>
+  </si>
+  <si>
+    <t>bogi emxq whwo gyoj</t>
+  </si>
+  <si>
+    <t>Suryakanth Jonnalagadda</t>
+  </si>
+  <si>
+    <t>suryakanth.customersuccess@gmail.com</t>
+  </si>
+  <si>
+    <t>mtxg bnxn zqig syxi</t>
+  </si>
+  <si>
+    <t>Rohan Benhal</t>
+  </si>
+  <si>
+    <t>benhalrohan@gmail.com</t>
+  </si>
+  <si>
+    <t>otra bwcm jbqt kqnn</t>
+  </si>
+  <si>
+    <t>Hansil Patel</t>
+  </si>
+  <si>
+    <t>hansilpatel86@gmail.com</t>
+  </si>
+  <si>
+    <t>hdse wqcr ammx ojua</t>
+  </si>
+  <si>
+    <t>Harshil sanghavi</t>
+  </si>
+  <si>
+    <t>harshilsanghavi86@gmail.com</t>
+  </si>
+  <si>
+    <t>ushx vneq bsdw ikxi</t>
+  </si>
+  <si>
+    <t>Rishi Rudrabhatla</t>
+  </si>
+  <si>
+    <t>Rishirudrabhatla45@gmail.com</t>
+  </si>
+  <si>
+    <t>ixqt ympe sklg zcqq</t>
+  </si>
+  <si>
+    <t>Nithish Kumar Reddy</t>
+  </si>
+  <si>
+    <t>nithishthigala@gmail.com</t>
+  </si>
+  <si>
+    <t>vkjg nmzf wtmd hvsy</t>
+  </si>
+  <si>
+    <t>hari krishna chirumamilla</t>
+  </si>
+  <si>
+    <t>harifullstack.dev27@gmail.com</t>
+  </si>
+  <si>
+    <t>eqor lgmp ggge pedt</t>
+  </si>
+  <si>
+    <t>charan yalamuri</t>
+  </si>
+  <si>
+    <t>venkatcharanyalamuri@gmail.com</t>
+  </si>
+  <si>
+    <t>ztoe eyzp fjzj oret</t>
+  </si>
+  <si>
+    <t>Vishal Balaji</t>
+  </si>
+  <si>
+    <t>balajigithendra2025@gmail.com</t>
+  </si>
+  <si>
+    <t>jsip wxmf vuyy xnqx</t>
+  </si>
+  <si>
+    <t>Prasanna</t>
+  </si>
+  <si>
+    <t>pathuriprasanna226@gmail.com</t>
+  </si>
+  <si>
+    <t>flhr csfb xius sjwn</t>
+  </si>
+  <si>
+    <t>shreelaasya</t>
+  </si>
+  <si>
+    <t>vshreelaasya5@gmail.com</t>
+  </si>
+  <si>
+    <t>fofz liww lbwy jgrg</t>
+  </si>
+  <si>
+    <t>Naveen</t>
+  </si>
+  <si>
+    <t>naveenkumarl1361@gmail.com</t>
+  </si>
+  <si>
+    <t>hhdj zufw vqij kywp</t>
+  </si>
+  <si>
+    <t>MIRZA ASGAR ALI</t>
+  </si>
+  <si>
+    <t>aliasgar.fs10@gmail.com</t>
+  </si>
+  <si>
+    <t>ejyf npkv bndz cnmg</t>
+  </si>
+  <si>
+    <t>Aashish Hemanth Masuna</t>
+  </si>
+  <si>
+    <t>ashishhemanth1@gmail.com</t>
+  </si>
+  <si>
+    <t>onim zsab qctw etxb</t>
   </si>
 </sst>
 </file>
@@ -387,12 +1456,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -408,27 +1477,1464 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>236</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>237</v>
       </c>
       <c r="C2" t="s">
-        <v>5</v>
+        <v>238</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>239</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>240</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>241</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>242</v>
+      </c>
+      <c r="B4" t="s">
+        <v>243</v>
+      </c>
+      <c r="C4" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>245</v>
+      </c>
+      <c r="B5" t="s">
+        <v>246</v>
+      </c>
+      <c r="C5" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>286</v>
+      </c>
+      <c r="B6" t="s">
+        <v>287</v>
+      </c>
+      <c r="C6" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>289</v>
+      </c>
+      <c r="B7" t="s">
+        <v>290</v>
+      </c>
+      <c r="C7" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>292</v>
+      </c>
+      <c r="B8" t="s">
+        <v>293</v>
+      </c>
+      <c r="C8" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>295</v>
+      </c>
+      <c r="B9" t="s">
+        <v>296</v>
+      </c>
+      <c r="C9" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>298</v>
+      </c>
+      <c r="B10" t="s">
+        <v>299</v>
+      </c>
+      <c r="C10" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>301</v>
+      </c>
+      <c r="B11" t="s">
+        <v>302</v>
+      </c>
+      <c r="C11" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>304</v>
+      </c>
+      <c r="B12" t="s">
+        <v>305</v>
+      </c>
+      <c r="C12" t="s">
+        <v>306</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C93615BE-0499-449D-BF80-AA6F427FA5DC}">
+  <dimension ref="A1:C121"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" t="s">
+        <v>45</v>
+      </c>
+      <c r="C15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>50</v>
+      </c>
+      <c r="B17" t="s">
+        <v>51</v>
+      </c>
+      <c r="C17" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>53</v>
+      </c>
+      <c r="B18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C18" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>56</v>
+      </c>
+      <c r="B19" t="s">
+        <v>57</v>
+      </c>
+      <c r="C19" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" t="s">
+        <v>60</v>
+      </c>
+      <c r="C20" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>62</v>
+      </c>
+      <c r="B21" t="s">
+        <v>63</v>
+      </c>
+      <c r="C21" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>65</v>
+      </c>
+      <c r="B22" t="s">
+        <v>66</v>
+      </c>
+      <c r="C22" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>68</v>
+      </c>
+      <c r="B23" t="s">
+        <v>69</v>
+      </c>
+      <c r="C23" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>71</v>
+      </c>
+      <c r="B24" t="s">
+        <v>72</v>
+      </c>
+      <c r="C24" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>74</v>
+      </c>
+      <c r="B25" t="s">
+        <v>75</v>
+      </c>
+      <c r="C25" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>77</v>
+      </c>
+      <c r="B26" t="s">
+        <v>78</v>
+      </c>
+      <c r="C26" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>80</v>
+      </c>
+      <c r="B27" t="s">
+        <v>81</v>
+      </c>
+      <c r="C27" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>83</v>
+      </c>
+      <c r="B28" t="s">
+        <v>84</v>
+      </c>
+      <c r="C28" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>86</v>
+      </c>
+      <c r="B29" t="s">
+        <v>87</v>
+      </c>
+      <c r="C29" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>89</v>
+      </c>
+      <c r="B30" t="s">
+        <v>90</v>
+      </c>
+      <c r="C30" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>92</v>
+      </c>
+      <c r="B31" t="s">
+        <v>93</v>
+      </c>
+      <c r="C31" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>95</v>
+      </c>
+      <c r="B32" t="s">
+        <v>96</v>
+      </c>
+      <c r="C32" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>98</v>
+      </c>
+      <c r="B33" t="s">
+        <v>99</v>
+      </c>
+      <c r="C33" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>101</v>
+      </c>
+      <c r="B34" t="s">
+        <v>102</v>
+      </c>
+      <c r="C34" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>104</v>
+      </c>
+      <c r="B35" t="s">
+        <v>105</v>
+      </c>
+      <c r="C35" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>107</v>
+      </c>
+      <c r="B36" t="s">
+        <v>108</v>
+      </c>
+      <c r="C36" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>110</v>
+      </c>
+      <c r="B37" t="s">
+        <v>111</v>
+      </c>
+      <c r="C37" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>113</v>
+      </c>
+      <c r="B38" t="s">
+        <v>114</v>
+      </c>
+      <c r="C38" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>116</v>
+      </c>
+      <c r="B39" t="s">
+        <v>117</v>
+      </c>
+      <c r="C39" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>119</v>
+      </c>
+      <c r="B40" t="s">
+        <v>120</v>
+      </c>
+      <c r="C40" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>122</v>
+      </c>
+      <c r="B41" t="s">
+        <v>123</v>
+      </c>
+      <c r="C41" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>125</v>
+      </c>
+      <c r="B42" t="s">
+        <v>126</v>
+      </c>
+      <c r="C42" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>128</v>
+      </c>
+      <c r="B43" t="s">
+        <v>129</v>
+      </c>
+      <c r="C43" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>131</v>
+      </c>
+      <c r="B44" t="s">
+        <v>132</v>
+      </c>
+      <c r="C44" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>134</v>
+      </c>
+      <c r="B45" t="s">
+        <v>135</v>
+      </c>
+      <c r="C45" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>137</v>
+      </c>
+      <c r="B46" t="s">
+        <v>138</v>
+      </c>
+      <c r="C46" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>140</v>
+      </c>
+      <c r="B47" t="s">
+        <v>141</v>
+      </c>
+      <c r="C47" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>143</v>
+      </c>
+      <c r="B48" t="s">
+        <v>144</v>
+      </c>
+      <c r="C48" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>146</v>
+      </c>
+      <c r="B49" t="s">
+        <v>147</v>
+      </c>
+      <c r="C49" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>149</v>
+      </c>
+      <c r="B50" t="s">
+        <v>150</v>
+      </c>
+      <c r="C50" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>152</v>
+      </c>
+      <c r="B51" t="s">
+        <v>153</v>
+      </c>
+      <c r="C51" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>155</v>
+      </c>
+      <c r="B52" t="s">
+        <v>156</v>
+      </c>
+      <c r="C52" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>158</v>
+      </c>
+      <c r="B53" t="s">
+        <v>159</v>
+      </c>
+      <c r="C53" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>161</v>
+      </c>
+      <c r="B54" t="s">
+        <v>162</v>
+      </c>
+      <c r="C54" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>164</v>
+      </c>
+      <c r="B55" t="s">
+        <v>165</v>
+      </c>
+      <c r="C55" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>167</v>
+      </c>
+      <c r="B56" t="s">
+        <v>168</v>
+      </c>
+      <c r="C56" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>170</v>
+      </c>
+      <c r="B57" t="s">
+        <v>171</v>
+      </c>
+      <c r="C57" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>173</v>
+      </c>
+      <c r="B58" t="s">
+        <v>174</v>
+      </c>
+      <c r="C58" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>176</v>
+      </c>
+      <c r="B59" t="s">
+        <v>177</v>
+      </c>
+      <c r="C59" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>179</v>
+      </c>
+      <c r="B60" t="s">
+        <v>180</v>
+      </c>
+      <c r="C60" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>182</v>
+      </c>
+      <c r="B61" t="s">
+        <v>183</v>
+      </c>
+      <c r="C61" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>185</v>
+      </c>
+      <c r="B62" t="s">
+        <v>186</v>
+      </c>
+      <c r="C62" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>188</v>
+      </c>
+      <c r="B63" t="s">
+        <v>189</v>
+      </c>
+      <c r="C63" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>191</v>
+      </c>
+      <c r="B64" t="s">
+        <v>192</v>
+      </c>
+      <c r="C64" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>194</v>
+      </c>
+      <c r="B65" t="s">
+        <v>195</v>
+      </c>
+      <c r="C65" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>197</v>
+      </c>
+      <c r="B66" t="s">
+        <v>198</v>
+      </c>
+      <c r="C66" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>200</v>
+      </c>
+      <c r="B67" t="s">
+        <v>201</v>
+      </c>
+      <c r="C67" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>203</v>
+      </c>
+      <c r="B68" t="s">
+        <v>204</v>
+      </c>
+      <c r="C68" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>206</v>
+      </c>
+      <c r="B69" t="s">
+        <v>207</v>
+      </c>
+      <c r="C69" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>209</v>
+      </c>
+      <c r="B70" t="s">
+        <v>210</v>
+      </c>
+      <c r="C70" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>212</v>
+      </c>
+      <c r="B71" t="s">
+        <v>213</v>
+      </c>
+      <c r="C71" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>215</v>
+      </c>
+      <c r="B72" t="s">
+        <v>216</v>
+      </c>
+      <c r="C72" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>218</v>
+      </c>
+      <c r="B73" t="s">
+        <v>219</v>
+      </c>
+      <c r="C73" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>221</v>
+      </c>
+      <c r="B74" t="s">
+        <v>222</v>
+      </c>
+      <c r="C74" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>224</v>
+      </c>
+      <c r="B75" t="s">
+        <v>225</v>
+      </c>
+      <c r="C75" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>227</v>
+      </c>
+      <c r="B76" t="s">
+        <v>228</v>
+      </c>
+      <c r="C76" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>230</v>
+      </c>
+      <c r="B77" t="s">
+        <v>231</v>
+      </c>
+      <c r="C77" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>233</v>
+      </c>
+      <c r="B78" t="s">
+        <v>234</v>
+      </c>
+      <c r="C78" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>236</v>
+      </c>
+      <c r="B79" t="s">
+        <v>237</v>
+      </c>
+      <c r="C79" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>239</v>
+      </c>
+      <c r="B80" t="s">
+        <v>240</v>
+      </c>
+      <c r="C80" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>242</v>
+      </c>
+      <c r="B81" t="s">
+        <v>243</v>
+      </c>
+      <c r="C81" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>245</v>
+      </c>
+      <c r="B82" t="s">
+        <v>246</v>
+      </c>
+      <c r="C82" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>248</v>
+      </c>
+      <c r="B83" t="s">
+        <v>249</v>
+      </c>
+      <c r="C83" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>251</v>
+      </c>
+      <c r="B84" t="s">
+        <v>252</v>
+      </c>
+      <c r="C84" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>254</v>
+      </c>
+      <c r="B85" t="s">
+        <v>255</v>
+      </c>
+      <c r="C85" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>257</v>
+      </c>
+      <c r="B86" t="s">
+        <v>258</v>
+      </c>
+      <c r="C86" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>260</v>
+      </c>
+      <c r="B87" t="s">
+        <v>261</v>
+      </c>
+      <c r="C87" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>263</v>
+      </c>
+      <c r="B88" t="s">
+        <v>264</v>
+      </c>
+      <c r="C88" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>266</v>
+      </c>
+      <c r="B89" t="s">
+        <v>267</v>
+      </c>
+      <c r="C89" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>269</v>
+      </c>
+      <c r="B90" t="s">
+        <v>270</v>
+      </c>
+      <c r="C90" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>272</v>
+      </c>
+      <c r="B91" t="s">
+        <v>273</v>
+      </c>
+      <c r="C91" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>275</v>
+      </c>
+      <c r="B92" t="s">
+        <v>276</v>
+      </c>
+      <c r="C92" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>278</v>
+      </c>
+      <c r="B93" t="s">
+        <v>279</v>
+      </c>
+      <c r="C93" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>281</v>
+      </c>
+      <c r="B94" t="s">
+        <v>282</v>
+      </c>
+      <c r="C94" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>281</v>
+      </c>
+      <c r="B95" t="s">
+        <v>284</v>
+      </c>
+      <c r="C95" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>286</v>
+      </c>
+      <c r="B96" t="s">
+        <v>287</v>
+      </c>
+      <c r="C96" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>289</v>
+      </c>
+      <c r="B97" t="s">
+        <v>290</v>
+      </c>
+      <c r="C97" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>292</v>
+      </c>
+      <c r="B98" t="s">
+        <v>293</v>
+      </c>
+      <c r="C98" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>295</v>
+      </c>
+      <c r="B99" t="s">
+        <v>296</v>
+      </c>
+      <c r="C99" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>298</v>
+      </c>
+      <c r="B100" t="s">
+        <v>299</v>
+      </c>
+      <c r="C100" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>301</v>
+      </c>
+      <c r="B101" t="s">
+        <v>302</v>
+      </c>
+      <c r="C101" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>304</v>
+      </c>
+      <c r="B102" t="s">
+        <v>305</v>
+      </c>
+      <c r="C102" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>307</v>
+      </c>
+      <c r="B103" t="s">
+        <v>308</v>
+      </c>
+      <c r="C103" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>310</v>
+      </c>
+      <c r="B104" t="s">
+        <v>311</v>
+      </c>
+      <c r="C104" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>313</v>
+      </c>
+      <c r="B105" t="s">
+        <v>314</v>
+      </c>
+      <c r="C105" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>316</v>
+      </c>
+      <c r="B106" t="s">
+        <v>317</v>
+      </c>
+      <c r="C106" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>319</v>
+      </c>
+      <c r="B107" t="s">
+        <v>320</v>
+      </c>
+      <c r="C107" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>322</v>
+      </c>
+      <c r="B108" t="s">
+        <v>323</v>
+      </c>
+      <c r="C108" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>325</v>
+      </c>
+      <c r="B109" t="s">
+        <v>326</v>
+      </c>
+      <c r="C109" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>328</v>
+      </c>
+      <c r="B110" t="s">
+        <v>329</v>
+      </c>
+      <c r="C110" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>331</v>
+      </c>
+      <c r="B111" t="s">
+        <v>332</v>
+      </c>
+      <c r="C111" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>334</v>
+      </c>
+      <c r="B112" t="s">
+        <v>335</v>
+      </c>
+      <c r="C112" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>337</v>
+      </c>
+      <c r="B113" t="s">
+        <v>338</v>
+      </c>
+      <c r="C113" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>340</v>
+      </c>
+      <c r="B114" t="s">
+        <v>341</v>
+      </c>
+      <c r="C114" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>343</v>
+      </c>
+      <c r="B115" t="s">
+        <v>344</v>
+      </c>
+      <c r="C115" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>346</v>
+      </c>
+      <c r="B116" t="s">
+        <v>347</v>
+      </c>
+      <c r="C116" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>349</v>
+      </c>
+      <c r="B117" t="s">
+        <v>350</v>
+      </c>
+      <c r="C117" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>352</v>
+      </c>
+      <c r="B118" t="s">
+        <v>353</v>
+      </c>
+      <c r="C118" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>355</v>
+      </c>
+      <c r="B119" t="s">
+        <v>356</v>
+      </c>
+      <c r="C119" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>358</v>
+      </c>
+      <c r="B120" t="s">
+        <v>359</v>
+      </c>
+      <c r="C120" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>361</v>
+      </c>
+      <c r="B121" t="s">
+        <v>362</v>
+      </c>
+      <c r="C121" t="s">
+        <v>363</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/version1/data/Candidates.xlsx
+++ b/version1/data/Candidates.xlsx
@@ -8,20 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\keert\OneDrive\Desktop\KEERTHIRAJ\PROJECTS\Email-Automation\version1\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{668D60B6-C682-4F03-813D-DD123D4E2FF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CD41110-F69E-40B2-9156-3CE424223981}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Candidates" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="3" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="4" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="376">
   <si>
     <t>Name</t>
   </si>
@@ -1117,6 +1119,42 @@
   </si>
   <si>
     <t>onim zsab qctw etxb</t>
+  </si>
+  <si>
+    <t>Abdullah Solaiman</t>
+  </si>
+  <si>
+    <t>absolaiman92@gmail.com</t>
+  </si>
+  <si>
+    <t>ncbj jifh wtij bjod</t>
+  </si>
+  <si>
+    <t>Keerthi Lanka</t>
+  </si>
+  <si>
+    <t>keerthilanka87@gmail.com</t>
+  </si>
+  <si>
+    <t>inop oyzm wkac rjmo</t>
+  </si>
+  <si>
+    <t>Manvitha</t>
+  </si>
+  <si>
+    <t>m.srimanvitha27@gmail.com</t>
+  </si>
+  <si>
+    <t>rvnn lpic jzwh wkqr</t>
+  </si>
+  <si>
+    <t>Mehul</t>
+  </si>
+  <si>
+    <t>mehulkkumar86@gmail.com</t>
+  </si>
+  <si>
+    <t>kqds geuf kwom cbnr</t>
   </si>
 </sst>
 </file>
@@ -1456,7 +1494,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.5546875" bestFit="1" customWidth="1"/>
@@ -1477,123 +1515,46 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>236</v>
+        <v>364</v>
       </c>
       <c r="B2" t="s">
-        <v>237</v>
+        <v>365</v>
       </c>
       <c r="C2" t="s">
-        <v>238</v>
+        <v>366</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>239</v>
+        <v>367</v>
       </c>
       <c r="B3" t="s">
-        <v>240</v>
+        <v>368</v>
       </c>
       <c r="C3" t="s">
-        <v>241</v>
+        <v>369</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>242</v>
+        <v>370</v>
       </c>
       <c r="B4" t="s">
-        <v>243</v>
+        <v>371</v>
       </c>
       <c r="C4" t="s">
-        <v>244</v>
+        <v>372</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>245</v>
+        <v>373</v>
       </c>
       <c r="B5" t="s">
-        <v>246</v>
+        <v>374</v>
       </c>
       <c r="C5" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>286</v>
-      </c>
-      <c r="B6" t="s">
-        <v>287</v>
-      </c>
-      <c r="C6" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>289</v>
-      </c>
-      <c r="B7" t="s">
-        <v>290</v>
-      </c>
-      <c r="C7" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>292</v>
-      </c>
-      <c r="B8" t="s">
-        <v>293</v>
-      </c>
-      <c r="C8" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>295</v>
-      </c>
-      <c r="B9" t="s">
-        <v>296</v>
-      </c>
-      <c r="C9" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>298</v>
-      </c>
-      <c r="B10" t="s">
-        <v>299</v>
-      </c>
-      <c r="C10" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>301</v>
-      </c>
-      <c r="B11" t="s">
-        <v>302</v>
-      </c>
-      <c r="C11" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>304</v>
-      </c>
-      <c r="B12" t="s">
-        <v>305</v>
-      </c>
-      <c r="C12" t="s">
-        <v>306</v>
+        <v>375</v>
       </c>
     </row>
   </sheetData>
@@ -1602,6 +1563,146 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3444D549-B8D2-4ABB-BFAE-62045244F625}">
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>236</v>
+      </c>
+      <c r="B1" t="s">
+        <v>237</v>
+      </c>
+      <c r="C1" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>239</v>
+      </c>
+      <c r="B2" t="s">
+        <v>240</v>
+      </c>
+      <c r="C2" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>242</v>
+      </c>
+      <c r="B3" t="s">
+        <v>243</v>
+      </c>
+      <c r="C3" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>245</v>
+      </c>
+      <c r="B4" t="s">
+        <v>246</v>
+      </c>
+      <c r="C4" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>286</v>
+      </c>
+      <c r="B5" t="s">
+        <v>287</v>
+      </c>
+      <c r="C5" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>289</v>
+      </c>
+      <c r="B6" t="s">
+        <v>290</v>
+      </c>
+      <c r="C6" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>292</v>
+      </c>
+      <c r="B7" t="s">
+        <v>293</v>
+      </c>
+      <c r="C7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>295</v>
+      </c>
+      <c r="B8" t="s">
+        <v>296</v>
+      </c>
+      <c r="C8" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>298</v>
+      </c>
+      <c r="B9" t="s">
+        <v>299</v>
+      </c>
+      <c r="C9" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>301</v>
+      </c>
+      <c r="B10" t="s">
+        <v>302</v>
+      </c>
+      <c r="C10" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>304</v>
+      </c>
+      <c r="B11" t="s">
+        <v>305</v>
+      </c>
+      <c r="C11" t="s">
+        <v>306</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF1C4F62-221A-4E4F-8CC0-1166BF273412}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C93615BE-0499-449D-BF80-AA6F427FA5DC}">
   <dimension ref="A1:C121"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/version1/data/Candidates.xlsx
+++ b/version1/data/Candidates.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\keert\OneDrive\Desktop\KEERTHIRAJ\PROJECTS\Email-Automation\version1\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CD41110-F69E-40B2-9156-3CE424223981}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{246A3773-A501-41F4-96CE-76D4FAD702AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21690" yWindow="3150" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Candidates" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="376">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="760" uniqueCount="364">
   <si>
     <t>Name</t>
   </si>
@@ -1119,42 +1119,6 @@
   </si>
   <si>
     <t>onim zsab qctw etxb</t>
-  </si>
-  <si>
-    <t>Abdullah Solaiman</t>
-  </si>
-  <si>
-    <t>absolaiman92@gmail.com</t>
-  </si>
-  <si>
-    <t>ncbj jifh wtij bjod</t>
-  </si>
-  <si>
-    <t>Keerthi Lanka</t>
-  </si>
-  <si>
-    <t>keerthilanka87@gmail.com</t>
-  </si>
-  <si>
-    <t>inop oyzm wkac rjmo</t>
-  </si>
-  <si>
-    <t>Manvitha</t>
-  </si>
-  <si>
-    <t>m.srimanvitha27@gmail.com</t>
-  </si>
-  <si>
-    <t>rvnn lpic jzwh wkqr</t>
-  </si>
-  <si>
-    <t>Mehul</t>
-  </si>
-  <si>
-    <t>mehulkkumar86@gmail.com</t>
-  </si>
-  <si>
-    <t>kqds geuf kwom cbnr</t>
   </si>
 </sst>
 </file>
@@ -1494,15 +1458,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:C122"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1513,48 +1477,1332 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>364</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>365</v>
+        <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>367</v>
+        <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>368</v>
+        <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>370</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>371</v>
+        <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>373</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>374</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>375</v>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>50</v>
+      </c>
+      <c r="B18" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>53</v>
+      </c>
+      <c r="B19" t="s">
+        <v>54</v>
+      </c>
+      <c r="C19" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>56</v>
+      </c>
+      <c r="B20" t="s">
+        <v>57</v>
+      </c>
+      <c r="C20" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>59</v>
+      </c>
+      <c r="B21" t="s">
+        <v>60</v>
+      </c>
+      <c r="C21" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>62</v>
+      </c>
+      <c r="B22" t="s">
+        <v>63</v>
+      </c>
+      <c r="C22" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>65</v>
+      </c>
+      <c r="B23" t="s">
+        <v>66</v>
+      </c>
+      <c r="C23" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>68</v>
+      </c>
+      <c r="B24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C24" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>71</v>
+      </c>
+      <c r="B25" t="s">
+        <v>72</v>
+      </c>
+      <c r="C25" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>74</v>
+      </c>
+      <c r="B26" t="s">
+        <v>75</v>
+      </c>
+      <c r="C26" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>77</v>
+      </c>
+      <c r="B27" t="s">
+        <v>78</v>
+      </c>
+      <c r="C27" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>80</v>
+      </c>
+      <c r="B28" t="s">
+        <v>81</v>
+      </c>
+      <c r="C28" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>83</v>
+      </c>
+      <c r="B29" t="s">
+        <v>84</v>
+      </c>
+      <c r="C29" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>86</v>
+      </c>
+      <c r="B30" t="s">
+        <v>87</v>
+      </c>
+      <c r="C30" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>89</v>
+      </c>
+      <c r="B31" t="s">
+        <v>90</v>
+      </c>
+      <c r="C31" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>92</v>
+      </c>
+      <c r="B32" t="s">
+        <v>93</v>
+      </c>
+      <c r="C32" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>95</v>
+      </c>
+      <c r="B33" t="s">
+        <v>96</v>
+      </c>
+      <c r="C33" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>98</v>
+      </c>
+      <c r="B34" t="s">
+        <v>99</v>
+      </c>
+      <c r="C34" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>101</v>
+      </c>
+      <c r="B35" t="s">
+        <v>102</v>
+      </c>
+      <c r="C35" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>104</v>
+      </c>
+      <c r="B36" t="s">
+        <v>105</v>
+      </c>
+      <c r="C36" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>107</v>
+      </c>
+      <c r="B37" t="s">
+        <v>108</v>
+      </c>
+      <c r="C37" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>110</v>
+      </c>
+      <c r="B38" t="s">
+        <v>111</v>
+      </c>
+      <c r="C38" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>113</v>
+      </c>
+      <c r="B39" t="s">
+        <v>114</v>
+      </c>
+      <c r="C39" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>116</v>
+      </c>
+      <c r="B40" t="s">
+        <v>117</v>
+      </c>
+      <c r="C40" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>119</v>
+      </c>
+      <c r="B41" t="s">
+        <v>120</v>
+      </c>
+      <c r="C41" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>122</v>
+      </c>
+      <c r="B42" t="s">
+        <v>123</v>
+      </c>
+      <c r="C42" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>125</v>
+      </c>
+      <c r="B43" t="s">
+        <v>126</v>
+      </c>
+      <c r="C43" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>128</v>
+      </c>
+      <c r="B44" t="s">
+        <v>129</v>
+      </c>
+      <c r="C44" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>131</v>
+      </c>
+      <c r="B45" t="s">
+        <v>132</v>
+      </c>
+      <c r="C45" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>134</v>
+      </c>
+      <c r="B46" t="s">
+        <v>135</v>
+      </c>
+      <c r="C46" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>137</v>
+      </c>
+      <c r="B47" t="s">
+        <v>138</v>
+      </c>
+      <c r="C47" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>140</v>
+      </c>
+      <c r="B48" t="s">
+        <v>141</v>
+      </c>
+      <c r="C48" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>143</v>
+      </c>
+      <c r="B49" t="s">
+        <v>144</v>
+      </c>
+      <c r="C49" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>146</v>
+      </c>
+      <c r="B50" t="s">
+        <v>147</v>
+      </c>
+      <c r="C50" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>149</v>
+      </c>
+      <c r="B51" t="s">
+        <v>150</v>
+      </c>
+      <c r="C51" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>152</v>
+      </c>
+      <c r="B52" t="s">
+        <v>153</v>
+      </c>
+      <c r="C52" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>155</v>
+      </c>
+      <c r="B53" t="s">
+        <v>156</v>
+      </c>
+      <c r="C53" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>158</v>
+      </c>
+      <c r="B54" t="s">
+        <v>159</v>
+      </c>
+      <c r="C54" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>161</v>
+      </c>
+      <c r="B55" t="s">
+        <v>162</v>
+      </c>
+      <c r="C55" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>164</v>
+      </c>
+      <c r="B56" t="s">
+        <v>165</v>
+      </c>
+      <c r="C56" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>167</v>
+      </c>
+      <c r="B57" t="s">
+        <v>168</v>
+      </c>
+      <c r="C57" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>170</v>
+      </c>
+      <c r="B58" t="s">
+        <v>171</v>
+      </c>
+      <c r="C58" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>173</v>
+      </c>
+      <c r="B59" t="s">
+        <v>174</v>
+      </c>
+      <c r="C59" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>176</v>
+      </c>
+      <c r="B60" t="s">
+        <v>177</v>
+      </c>
+      <c r="C60" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>179</v>
+      </c>
+      <c r="B61" t="s">
+        <v>180</v>
+      </c>
+      <c r="C61" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>182</v>
+      </c>
+      <c r="B62" t="s">
+        <v>183</v>
+      </c>
+      <c r="C62" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>185</v>
+      </c>
+      <c r="B63" t="s">
+        <v>186</v>
+      </c>
+      <c r="C63" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>188</v>
+      </c>
+      <c r="B64" t="s">
+        <v>189</v>
+      </c>
+      <c r="C64" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>191</v>
+      </c>
+      <c r="B65" t="s">
+        <v>192</v>
+      </c>
+      <c r="C65" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>194</v>
+      </c>
+      <c r="B66" t="s">
+        <v>195</v>
+      </c>
+      <c r="C66" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>197</v>
+      </c>
+      <c r="B67" t="s">
+        <v>198</v>
+      </c>
+      <c r="C67" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>200</v>
+      </c>
+      <c r="B68" t="s">
+        <v>201</v>
+      </c>
+      <c r="C68" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>203</v>
+      </c>
+      <c r="B69" t="s">
+        <v>204</v>
+      </c>
+      <c r="C69" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>206</v>
+      </c>
+      <c r="B70" t="s">
+        <v>207</v>
+      </c>
+      <c r="C70" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>209</v>
+      </c>
+      <c r="B71" t="s">
+        <v>210</v>
+      </c>
+      <c r="C71" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>212</v>
+      </c>
+      <c r="B72" t="s">
+        <v>213</v>
+      </c>
+      <c r="C72" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>215</v>
+      </c>
+      <c r="B73" t="s">
+        <v>216</v>
+      </c>
+      <c r="C73" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>218</v>
+      </c>
+      <c r="B74" t="s">
+        <v>219</v>
+      </c>
+      <c r="C74" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>221</v>
+      </c>
+      <c r="B75" t="s">
+        <v>222</v>
+      </c>
+      <c r="C75" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>224</v>
+      </c>
+      <c r="B76" t="s">
+        <v>225</v>
+      </c>
+      <c r="C76" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>227</v>
+      </c>
+      <c r="B77" t="s">
+        <v>228</v>
+      </c>
+      <c r="C77" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>230</v>
+      </c>
+      <c r="B78" t="s">
+        <v>231</v>
+      </c>
+      <c r="C78" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>233</v>
+      </c>
+      <c r="B79" t="s">
+        <v>234</v>
+      </c>
+      <c r="C79" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>236</v>
+      </c>
+      <c r="B80" t="s">
+        <v>237</v>
+      </c>
+      <c r="C80" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>239</v>
+      </c>
+      <c r="B81" t="s">
+        <v>240</v>
+      </c>
+      <c r="C81" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>242</v>
+      </c>
+      <c r="B82" t="s">
+        <v>243</v>
+      </c>
+      <c r="C82" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>245</v>
+      </c>
+      <c r="B83" t="s">
+        <v>246</v>
+      </c>
+      <c r="C83" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>248</v>
+      </c>
+      <c r="B84" t="s">
+        <v>249</v>
+      </c>
+      <c r="C84" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>251</v>
+      </c>
+      <c r="B85" t="s">
+        <v>252</v>
+      </c>
+      <c r="C85" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>254</v>
+      </c>
+      <c r="B86" t="s">
+        <v>255</v>
+      </c>
+      <c r="C86" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>257</v>
+      </c>
+      <c r="B87" t="s">
+        <v>258</v>
+      </c>
+      <c r="C87" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>260</v>
+      </c>
+      <c r="B88" t="s">
+        <v>261</v>
+      </c>
+      <c r="C88" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>263</v>
+      </c>
+      <c r="B89" t="s">
+        <v>264</v>
+      </c>
+      <c r="C89" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>266</v>
+      </c>
+      <c r="B90" t="s">
+        <v>267</v>
+      </c>
+      <c r="C90" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>269</v>
+      </c>
+      <c r="B91" t="s">
+        <v>270</v>
+      </c>
+      <c r="C91" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>272</v>
+      </c>
+      <c r="B92" t="s">
+        <v>273</v>
+      </c>
+      <c r="C92" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>275</v>
+      </c>
+      <c r="B93" t="s">
+        <v>276</v>
+      </c>
+      <c r="C93" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>278</v>
+      </c>
+      <c r="B94" t="s">
+        <v>279</v>
+      </c>
+      <c r="C94" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>281</v>
+      </c>
+      <c r="B95" t="s">
+        <v>282</v>
+      </c>
+      <c r="C95" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>281</v>
+      </c>
+      <c r="B96" t="s">
+        <v>284</v>
+      </c>
+      <c r="C96" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>286</v>
+      </c>
+      <c r="B97" t="s">
+        <v>287</v>
+      </c>
+      <c r="C97" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>289</v>
+      </c>
+      <c r="B98" t="s">
+        <v>290</v>
+      </c>
+      <c r="C98" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>292</v>
+      </c>
+      <c r="B99" t="s">
+        <v>293</v>
+      </c>
+      <c r="C99" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>295</v>
+      </c>
+      <c r="B100" t="s">
+        <v>296</v>
+      </c>
+      <c r="C100" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>298</v>
+      </c>
+      <c r="B101" t="s">
+        <v>299</v>
+      </c>
+      <c r="C101" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>301</v>
+      </c>
+      <c r="B102" t="s">
+        <v>302</v>
+      </c>
+      <c r="C102" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>304</v>
+      </c>
+      <c r="B103" t="s">
+        <v>305</v>
+      </c>
+      <c r="C103" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>307</v>
+      </c>
+      <c r="B104" t="s">
+        <v>308</v>
+      </c>
+      <c r="C104" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>310</v>
+      </c>
+      <c r="B105" t="s">
+        <v>311</v>
+      </c>
+      <c r="C105" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>313</v>
+      </c>
+      <c r="B106" t="s">
+        <v>314</v>
+      </c>
+      <c r="C106" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>316</v>
+      </c>
+      <c r="B107" t="s">
+        <v>317</v>
+      </c>
+      <c r="C107" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>319</v>
+      </c>
+      <c r="B108" t="s">
+        <v>320</v>
+      </c>
+      <c r="C108" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>322</v>
+      </c>
+      <c r="B109" t="s">
+        <v>323</v>
+      </c>
+      <c r="C109" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>325</v>
+      </c>
+      <c r="B110" t="s">
+        <v>326</v>
+      </c>
+      <c r="C110" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>328</v>
+      </c>
+      <c r="B111" t="s">
+        <v>329</v>
+      </c>
+      <c r="C111" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>331</v>
+      </c>
+      <c r="B112" t="s">
+        <v>332</v>
+      </c>
+      <c r="C112" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>334</v>
+      </c>
+      <c r="B113" t="s">
+        <v>335</v>
+      </c>
+      <c r="C113" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>337</v>
+      </c>
+      <c r="B114" t="s">
+        <v>338</v>
+      </c>
+      <c r="C114" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>340</v>
+      </c>
+      <c r="B115" t="s">
+        <v>341</v>
+      </c>
+      <c r="C115" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>343</v>
+      </c>
+      <c r="B116" t="s">
+        <v>344</v>
+      </c>
+      <c r="C116" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>346</v>
+      </c>
+      <c r="B117" t="s">
+        <v>347</v>
+      </c>
+      <c r="C117" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>349</v>
+      </c>
+      <c r="B118" t="s">
+        <v>350</v>
+      </c>
+      <c r="C118" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>352</v>
+      </c>
+      <c r="B119" t="s">
+        <v>353</v>
+      </c>
+      <c r="C119" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>355</v>
+      </c>
+      <c r="B120" t="s">
+        <v>356</v>
+      </c>
+      <c r="C120" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>358</v>
+      </c>
+      <c r="B121" t="s">
+        <v>359</v>
+      </c>
+      <c r="C121" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>361</v>
+      </c>
+      <c r="B122" t="s">
+        <v>362</v>
+      </c>
+      <c r="C122" t="s">
+        <v>363</v>
       </c>
     </row>
   </sheetData>
@@ -1565,9 +2813,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3444D549-B8D2-4ABB-BFAE-62045244F625}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>236</v>
       </c>
@@ -1578,7 +2826,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>239</v>
       </c>
@@ -1589,7 +2837,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>242</v>
       </c>
@@ -1600,7 +2848,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>245</v>
       </c>
@@ -1611,7 +2859,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>286</v>
       </c>
@@ -1622,7 +2870,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>289</v>
       </c>
@@ -1633,7 +2881,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>292</v>
       </c>
@@ -1644,7 +2892,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>295</v>
       </c>
@@ -1655,7 +2903,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>298</v>
       </c>
@@ -1666,7 +2914,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>301</v>
       </c>
@@ -1677,7 +2925,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>304</v>
       </c>
@@ -1696,7 +2944,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF1C4F62-221A-4E4F-8CC0-1166BF273412}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1705,9 +2953,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C93615BE-0499-449D-BF80-AA6F427FA5DC}">
   <dimension ref="A1:C121"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -1718,7 +2966,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1729,7 +2977,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -1740,7 +2988,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -1751,7 +2999,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -1762,7 +3010,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -1770,7 +3018,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -1781,7 +3029,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -1792,7 +3040,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -1803,7 +3051,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -1814,7 +3062,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>32</v>
       </c>
@@ -1825,7 +3073,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>35</v>
       </c>
@@ -1836,7 +3084,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>38</v>
       </c>
@@ -1847,7 +3095,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>41</v>
       </c>
@@ -1858,7 +3106,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>44</v>
       </c>
@@ -1869,7 +3117,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>47</v>
       </c>
@@ -1880,7 +3128,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>50</v>
       </c>
@@ -1891,7 +3139,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>53</v>
       </c>
@@ -1902,7 +3150,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>56</v>
       </c>
@@ -1913,7 +3161,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>59</v>
       </c>
@@ -1924,7 +3172,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>62</v>
       </c>
@@ -1935,7 +3183,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>65</v>
       </c>
@@ -1946,7 +3194,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>68</v>
       </c>
@@ -1957,7 +3205,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>71</v>
       </c>
@@ -1968,7 +3216,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>74</v>
       </c>
@@ -1979,7 +3227,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>77</v>
       </c>
@@ -1990,7 +3238,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>80</v>
       </c>
@@ -2001,7 +3249,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>83</v>
       </c>
@@ -2012,7 +3260,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>86</v>
       </c>
@@ -2023,7 +3271,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>89</v>
       </c>
@@ -2034,7 +3282,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>92</v>
       </c>
@@ -2045,7 +3293,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>95</v>
       </c>
@@ -2056,7 +3304,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>98</v>
       </c>
@@ -2067,7 +3315,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>101</v>
       </c>
@@ -2078,7 +3326,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>104</v>
       </c>
@@ -2089,7 +3337,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>107</v>
       </c>
@@ -2100,7 +3348,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>110</v>
       </c>
@@ -2111,7 +3359,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>113</v>
       </c>
@@ -2122,7 +3370,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>116</v>
       </c>
@@ -2133,7 +3381,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>119</v>
       </c>
@@ -2144,7 +3392,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>122</v>
       </c>
@@ -2155,7 +3403,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>125</v>
       </c>
@@ -2166,7 +3414,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>128</v>
       </c>
@@ -2177,7 +3425,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>131</v>
       </c>
@@ -2188,7 +3436,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>134</v>
       </c>
@@ -2199,7 +3447,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>137</v>
       </c>
@@ -2210,7 +3458,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>140</v>
       </c>
@@ -2221,7 +3469,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>143</v>
       </c>
@@ -2232,7 +3480,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>146</v>
       </c>
@@ -2243,7 +3491,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>149</v>
       </c>
@@ -2254,7 +3502,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>152</v>
       </c>
@@ -2265,7 +3513,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>155</v>
       </c>
@@ -2276,7 +3524,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>158</v>
       </c>
@@ -2287,7 +3535,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>161</v>
       </c>
@@ -2298,7 +3546,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>164</v>
       </c>
@@ -2309,7 +3557,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>167</v>
       </c>
@@ -2320,7 +3568,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>170</v>
       </c>
@@ -2331,7 +3579,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>173</v>
       </c>
@@ -2342,7 +3590,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>176</v>
       </c>
@@ -2353,7 +3601,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>179</v>
       </c>
@@ -2364,7 +3612,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>182</v>
       </c>
@@ -2375,7 +3623,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>185</v>
       </c>
@@ -2386,7 +3634,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>188</v>
       </c>
@@ -2397,7 +3645,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>191</v>
       </c>
@@ -2408,7 +3656,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>194</v>
       </c>
@@ -2419,7 +3667,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>197</v>
       </c>
@@ -2430,7 +3678,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>200</v>
       </c>
@@ -2441,7 +3689,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>203</v>
       </c>
@@ -2452,7 +3700,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>206</v>
       </c>
@@ -2463,7 +3711,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>209</v>
       </c>
@@ -2474,7 +3722,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>212</v>
       </c>
@@ -2485,7 +3733,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>215</v>
       </c>
@@ -2496,7 +3744,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>218</v>
       </c>
@@ -2507,7 +3755,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>221</v>
       </c>
@@ -2518,7 +3766,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>224</v>
       </c>
@@ -2529,7 +3777,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>227</v>
       </c>
@@ -2540,7 +3788,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>230</v>
       </c>
@@ -2551,7 +3799,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>233</v>
       </c>
@@ -2562,7 +3810,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>236</v>
       </c>
@@ -2573,7 +3821,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>239</v>
       </c>
@@ -2584,7 +3832,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>242</v>
       </c>
@@ -2595,7 +3843,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>245</v>
       </c>
@@ -2606,7 +3854,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>248</v>
       </c>
@@ -2617,7 +3865,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>251</v>
       </c>
@@ -2628,7 +3876,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>254</v>
       </c>
@@ -2639,7 +3887,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>257</v>
       </c>
@@ -2650,7 +3898,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>260</v>
       </c>
@@ -2661,7 +3909,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>263</v>
       </c>
@@ -2672,7 +3920,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>266</v>
       </c>
@@ -2683,7 +3931,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>269</v>
       </c>
@@ -2694,7 +3942,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>272</v>
       </c>
@@ -2705,7 +3953,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>275</v>
       </c>
@@ -2716,7 +3964,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>278</v>
       </c>
@@ -2727,7 +3975,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>281</v>
       </c>
@@ -2738,7 +3986,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>281</v>
       </c>
@@ -2749,7 +3997,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>286</v>
       </c>
@@ -2760,7 +4008,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>289</v>
       </c>
@@ -2771,7 +4019,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>292</v>
       </c>
@@ -2782,7 +4030,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>295</v>
       </c>
@@ -2793,7 +4041,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>298</v>
       </c>
@@ -2804,7 +4052,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>301</v>
       </c>
@@ -2815,7 +4063,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>304</v>
       </c>
@@ -2826,7 +4074,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>307</v>
       </c>
@@ -2837,7 +4085,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>310</v>
       </c>
@@ -2848,7 +4096,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>313</v>
       </c>
@@ -2859,7 +4107,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>316</v>
       </c>
@@ -2870,7 +4118,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>319</v>
       </c>
@@ -2881,7 +4129,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>322</v>
       </c>
@@ -2892,7 +4140,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>325</v>
       </c>
@@ -2903,7 +4151,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>328</v>
       </c>
@@ -2914,7 +4162,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>331</v>
       </c>
@@ -2925,7 +4173,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>334</v>
       </c>
@@ -2936,7 +4184,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>337</v>
       </c>
@@ -2947,7 +4195,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>340</v>
       </c>
@@ -2958,7 +4206,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>343</v>
       </c>
@@ -2969,7 +4217,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>346</v>
       </c>
@@ -2980,7 +4228,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>349</v>
       </c>
@@ -2991,7 +4239,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>352</v>
       </c>
@@ -3002,7 +4250,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>355</v>
       </c>
@@ -3013,7 +4261,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>358</v>
       </c>
@@ -3024,7 +4272,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>361</v>
       </c>
